--- a/app/static/templates/excel/template_grammar.xlsx
+++ b/app/static/templates/excel/template_grammar.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Grammar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grammar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/app/static/templates/excel/template_grammar.xlsx
+++ b/app/static/templates/excel/template_grammar.xlsx
@@ -449,18 +449,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,25 +491,50 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>order_index</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>exam_targets</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>toeic_parts</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>toeic_weight</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>importance</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>rule_explanation</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>examples_json</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>common_mistakes</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>tips_tricks</t>
         </is>
@@ -518,7 +548,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Các thì (Tenses)</t>
+          <t>Thì (Tenses)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -531,12 +561,35 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>General English, TOEIC, IELTS</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Part 5, Part 6</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Diễn tả hành động đã xảy ra trong quá khứ nhưng có kết quả hoặc liên quan mật thiết đến hiện tại.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>1. CÔNG THỨC KHẲNG ĐỊNH:
 S + have / has + V3/ed + (O)
@@ -546,18 +599,18 @@
 Have / Has + S + V3/ed...?</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>I have lived in Hanoi for 5 years.|Tôi đã sống ở Hà Nội được 5 năm.
 She has already finished her homework.|Cô ấy đã làm xong bài tập về nhà rồi.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Nhầm lẫn giữa Thì Quá Khứ Đơn (Past Simple - có thời gian xác định cụ thể trong quá khứ như yesterday, in 2020) và Hiện Tại Hoàn Thành.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Dấu hiệu nhận biết đặc trưng: since, for, already, yet, just, ever, never, so far, up to now.</t>
         </is>
@@ -571,7 +624,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Câu điều kiện (Conditionals)</t>
+          <t>Cấu trúc câu nâng cao (Advanced Structures)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -584,29 +637,52 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>General English, TOEIC, IELTS, THPT</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Part 5, Part 6</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Diễn tả giả định trái ngược với thực tế ở hiện tại hoặc khó có thể xảy ra.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Mệnh đề If: If + S + V2/ed (động từ to be dùng 'were' cho mọi ngôi)
 Mệnh đề chính: S + would / could + V_inf</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>If I were you, I would accept the job offer.|Nếu tôi là bạn, tôi sẽ nhận lời đề nghị làm việc đó.
 If he had more money, he would travel around the world.|Nếu anh ấy có nhiều tiền hơn, anh ấy sẽ đi du lịch vòng quanh thế giới.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Dùng 'was' thay vì 'were' trong các bài thi trang trọng (Formal English quy định dùng 'were').</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Hãy nhớ câu cửa miệng: 'If I were you, I would...' để luôn nhớ chia 'were' và 'would + V_inf'.</t>
         </is>
